--- a/output/pdf_financials_xlsx/ERD.xlsx
+++ b/output/pdf_financials_xlsx/ERD.xlsx
@@ -1315,10 +1315,10 @@
         </is>
       </c>
       <c r="B16" s="3" t="n">
-        <v>3592.391</v>
+        <v>-3592.391</v>
       </c>
       <c r="C16" s="3" t="n">
-        <v>2177.057</v>
+        <v>-2177.057</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>-4.689972</v>
@@ -1327,46 +1327,46 @@
         <v>-13.761548</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>7.34581</v>
+        <v>-7.34581</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>2.760423</v>
+        <v>-2.760423</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>2.616553</v>
+        <v>-2.616553</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>12.607625</v>
+        <v>-12.607625</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>2.499739</v>
+        <v>-2.499739</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>4.027465</v>
+        <v>-4.027465</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>3.65699</v>
+        <v>-3.65699</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>2.683292</v>
+        <v>-2.683292</v>
       </c>
       <c r="N16" s="3" t="n">
-        <v>13.116358</v>
+        <v>-13.116358</v>
       </c>
       <c r="O16" s="3" t="n">
-        <v>5.570523</v>
+        <v>-5.570523</v>
       </c>
       <c r="P16" s="3" t="n">
-        <v>5.986237</v>
+        <v>-5.986237</v>
       </c>
       <c r="Q16" s="3" t="n">
         <v>-0.522043</v>
       </c>
       <c r="R16" s="3" t="n">
-        <v>8.245886</v>
+        <v>-8.245886</v>
       </c>
       <c r="S16" s="3" t="n">
-        <v>8.181842</v>
+        <v>-8.181842</v>
       </c>
     </row>
     <row r="17">
@@ -1631,10 +1631,10 @@
         </is>
       </c>
       <c r="B20" s="3" t="n">
-        <v>3592.391</v>
+        <v>-3592.391</v>
       </c>
       <c r="C20" s="3" t="n">
-        <v>2177.057</v>
+        <v>-2177.057</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>-4.651687</v>
@@ -1643,46 +1643,46 @@
         <v>-13.758371</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>7.34581</v>
+        <v>-7.34581</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>2.760423</v>
+        <v>-2.760423</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>2.616553</v>
+        <v>-2.616553</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>12.607625</v>
+        <v>-12.607625</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>2.499739</v>
+        <v>-2.499739</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>4.027465</v>
+        <v>-4.027465</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>3.65699</v>
+        <v>-3.65699</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>2.683292</v>
+        <v>-2.683292</v>
       </c>
       <c r="N20" s="3" t="n">
-        <v>13.116358</v>
+        <v>-13.116358</v>
       </c>
       <c r="O20" s="3" t="n">
-        <v>5.570523</v>
+        <v>-5.570523</v>
       </c>
       <c r="P20" s="3" t="n">
-        <v>5.986237</v>
+        <v>-5.986237</v>
       </c>
       <c r="Q20" s="3" t="n">
         <v>-0.522043</v>
       </c>
       <c r="R20" s="3" t="n">
-        <v>8.245886</v>
+        <v>-8.245886</v>
       </c>
       <c r="S20" s="3" t="n">
-        <v>8.181842</v>
+        <v>-8.181842</v>
       </c>
     </row>
     <row r="21">
@@ -1814,10 +1814,10 @@
         </is>
       </c>
       <c r="B23" s="3" t="n">
-        <v>3592.391</v>
+        <v>-3592.391</v>
       </c>
       <c r="C23" s="3" t="n">
-        <v>2177.057</v>
+        <v>-2177.057</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>-4.651687</v>
@@ -1826,46 +1826,46 @@
         <v>-13.758371</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>7.34581</v>
+        <v>-7.34581</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>2.760423</v>
+        <v>-2.760423</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>2.616553</v>
+        <v>-2.616553</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>12.607625</v>
+        <v>-12.607625</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>2.499739</v>
+        <v>-2.499739</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>4.027465</v>
+        <v>-4.027465</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>3.65699</v>
+        <v>-3.65699</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>2.683292</v>
+        <v>-2.683292</v>
       </c>
       <c r="N23" s="3" t="n">
-        <v>13.116358</v>
+        <v>-13.116358</v>
       </c>
       <c r="O23" s="3" t="n">
-        <v>5.570523</v>
+        <v>-5.570523</v>
       </c>
       <c r="P23" s="3" t="n">
-        <v>5.986237</v>
+        <v>-5.986237</v>
       </c>
       <c r="Q23" s="3" t="n">
         <v>-0.522043</v>
       </c>
       <c r="R23" s="3" t="n">
-        <v>8.245886</v>
+        <v>-8.245886</v>
       </c>
       <c r="S23" s="3" t="n">
-        <v>8.181842</v>
+        <v>-8.181842</v>
       </c>
     </row>
     <row r="24">
@@ -2001,10 +2001,10 @@
         </is>
       </c>
       <c r="B26" s="3" t="n">
-        <v>89809.77499999999</v>
+        <v>-89809.77499999999</v>
       </c>
       <c r="C26" s="3" t="n">
-        <v>108852.85</v>
+        <v>-108852.85</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>93.03373999999999</v>
@@ -2013,37 +2013,37 @@
         <v>105.833623</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>48.972067</v>
+        <v>-48.972067</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>55.20846</v>
+        <v>-55.20846</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>65.413825</v>
+        <v>-65.413825</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>90.054464</v>
+        <v>-90.054464</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>124.98695</v>
+        <v>-124.98695</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>134.248833</v>
+        <v>-134.248833</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>182.8495</v>
+        <v>-182.8495</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>134.1646</v>
+        <v>-134.1646</v>
       </c>
       <c r="N26" s="3" t="n">
-        <v>218.605967</v>
+        <v>-218.605967</v>
       </c>
       <c r="O26" s="3" t="n">
-        <v>278.52615</v>
+        <v>-278.52615</v>
       </c>
       <c r="P26" s="3" t="n">
-        <v>299.31185</v>
+        <v>-299.31185</v>
       </c>
       <c r="Q26" s="1" t="inlineStr">
         <is>
@@ -2051,10 +2051,10 @@
         </is>
       </c>
       <c r="R26" s="3" t="n">
-        <v>58.899186</v>
+        <v>-58.899186</v>
       </c>
       <c r="S26" s="3" t="n">
-        <v>62.937246</v>
+        <v>-62.937246</v>
       </c>
     </row>
     <row r="27">
@@ -2064,10 +2064,10 @@
         </is>
       </c>
       <c r="B27" s="3" t="n">
-        <v>3592.391</v>
+        <v>-3592.391</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>2177.057</v>
+        <v>-2177.057</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>-4.960507</v>
@@ -2076,46 +2076,46 @@
         <v>-13.843796</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>7.249428</v>
+        <v>-7.442192</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>2.751633</v>
+        <v>-2.769213</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>2.613617</v>
+        <v>-2.619489</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>12.602699</v>
+        <v>-12.612551</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>2.487784</v>
+        <v>-2.511694</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>4.11897</v>
+        <v>-3.93596</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>3.707806</v>
+        <v>-3.606174</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>2.719804</v>
+        <v>-2.64678</v>
       </c>
       <c r="N27" s="3" t="n">
-        <v>13.179216</v>
+        <v>-13.0535</v>
       </c>
       <c r="O27" s="3" t="n">
-        <v>5.625538</v>
+        <v>-5.515508</v>
       </c>
       <c r="P27" s="3" t="n">
-        <v>6.04462</v>
+        <v>-5.927854</v>
       </c>
       <c r="Q27" s="3" t="n">
         <v>-0.252434</v>
       </c>
       <c r="R27" s="3" t="n">
-        <v>8.410147</v>
+        <v>-8.081625000000001</v>
       </c>
       <c r="S27" s="3" t="n">
-        <v>8.370107000000001</v>
+        <v>-7.993577</v>
       </c>
     </row>
     <row r="28">
@@ -2186,10 +2186,10 @@
         </is>
       </c>
       <c r="B29" s="3" t="n">
-        <v>3679.027</v>
+        <v>-3505.755</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>2493.272</v>
+        <v>-1860.842</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>-4.59359</v>
@@ -2198,46 +2198,46 @@
         <v>-13.525094</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>7.286983</v>
+        <v>-7.404637</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>2.78072</v>
+        <v>-2.740126</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>2.633931</v>
+        <v>-2.599175</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>12.619346</v>
+        <v>-12.595904</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>2.502693</v>
+        <v>-2.496785</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>4.137255</v>
+        <v>-3.917675</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>3.72871</v>
+        <v>-3.58527</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>2.752052</v>
+        <v>-2.614532</v>
       </c>
       <c r="N29" s="3" t="n">
-        <v>13.233607</v>
+        <v>-12.999109</v>
       </c>
       <c r="O29" s="3" t="n">
-        <v>5.707986</v>
+        <v>-5.43306</v>
       </c>
       <c r="P29" s="3" t="n">
-        <v>6.1812</v>
+        <v>-5.791274</v>
       </c>
       <c r="Q29" s="3" t="n">
         <v>-0.215475</v>
       </c>
       <c r="R29" s="3" t="n">
-        <v>8.439975</v>
+        <v>-8.051797000000001</v>
       </c>
       <c r="S29" s="3" t="n">
-        <v>8.39629</v>
+        <v>-7.967394</v>
       </c>
     </row>
     <row r="30">
@@ -2340,10 +2340,10 @@
         </is>
       </c>
       <c r="B31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>-0.8163161741690569</v>
@@ -2352,46 +2352,46 @@
         <v>-0.02308606560831674</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="N31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="O31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="P31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="Q31" s="3" t="n">
         <v>-0</v>
       </c>
       <c r="R31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="S31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -45251,22 +45251,22 @@
         </is>
       </c>
       <c r="N351" s="5" t="n">
-        <v>4.027465</v>
+        <v>-4.027465</v>
       </c>
       <c r="O351" s="5" t="n">
-        <v>3.65699</v>
+        <v>-3.65699</v>
       </c>
       <c r="P351" s="5" t="n">
-        <v>2.683292</v>
+        <v>-2.683292</v>
       </c>
       <c r="Q351" s="5" t="n">
-        <v>13.116358</v>
+        <v>-13.116358</v>
       </c>
       <c r="R351" s="5" t="n">
-        <v>5.570523</v>
+        <v>-5.570523</v>
       </c>
       <c r="S351" s="5" t="n">
-        <v>5.986237</v>
+        <v>-5.986237</v>
       </c>
       <c r="T351" t="inlineStr">
         <is>
@@ -45274,10 +45274,10 @@
         </is>
       </c>
       <c r="U351" s="5" t="n">
-        <v>8.245886</v>
+        <v>-8.245886</v>
       </c>
       <c r="V351" s="5" t="n">
-        <v>8.181842</v>
+        <v>-8.181842</v>
       </c>
     </row>
     <row r="352">
@@ -49498,22 +49498,22 @@
         <v>-13.758371</v>
       </c>
       <c r="I393" s="5" t="n">
-        <v>7.34581</v>
+        <v>-7.34581</v>
       </c>
       <c r="J393" s="5" t="n">
-        <v>2.760423</v>
+        <v>-2.760423</v>
       </c>
       <c r="K393" s="5" t="n">
-        <v>2.616553</v>
+        <v>-2.616553</v>
       </c>
       <c r="L393" s="5" t="n">
-        <v>12.607625</v>
+        <v>-12.607625</v>
       </c>
       <c r="M393" s="5" t="n">
-        <v>2.499739</v>
+        <v>-2.499739</v>
       </c>
       <c r="N393" s="5" t="n">
-        <v>4.027465</v>
+        <v>-4.027465</v>
       </c>
       <c r="O393" t="inlineStr">
         <is>
@@ -60456,10 +60456,10 @@
         </is>
       </c>
       <c r="E499" s="5" t="n">
-        <v>3592.391</v>
+        <v>-3592.391</v>
       </c>
       <c r="F499" s="5" t="n">
-        <v>2177.057</v>
+        <v>-2177.057</v>
       </c>
       <c r="G499" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/ERD.xlsx
+++ b/output/pdf_financials_xlsx/ERD.xlsx
@@ -2007,28 +2007,28 @@
         <v>-108852.85</v>
       </c>
       <c r="D26" s="3" t="n">
-        <v>93.03373999999999</v>
+        <v>89.257772</v>
       </c>
       <c r="E26" s="3" t="n">
-        <v>105.833623</v>
+        <v>45.363318</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>-48.972067</v>
+        <v>48.094528</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>-55.20846</v>
+        <v>58.704258</v>
       </c>
       <c r="H26" s="3" t="n">
-        <v>-65.413825</v>
+        <v>74.25541699999999</v>
       </c>
       <c r="I26" s="3" t="n">
-        <v>-90.054464</v>
+        <v>92.590453</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>-124.98695</v>
+        <v>117.127676</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>-134.248833</v>
+        <v>142.916756</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>-182.8495</v>
@@ -2510,19 +2510,19 @@
         <v>13.764186</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>8.37923</v>
+        <v>4.10435</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>1.502889</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.569469</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.136824</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.67579</v>
       </c>
       <c r="J34" s="3" t="n">
         <v>1.071209</v>
@@ -2632,19 +2632,19 @@
         <v>13.764186</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>8.37923</v>
+        <v>4.10435</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>1.502889</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.569469</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.136824</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.67579</v>
       </c>
       <c r="J36" s="3" t="n">
         <v>1.071209</v>
@@ -3364,19 +3364,19 @@
         <v>0.313165</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0</v>
+        <v>0.070259</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>1.541992</v>
+        <v>0.039103</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.582098</v>
+        <v>0.012629</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.152804</v>
+        <v>0.01598</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.692967</v>
+        <v>0.017177</v>
       </c>
       <c r="J48" s="3" t="n">
         <v>0.039743</v>
@@ -16652,7 +16652,7 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -44900,7 +44900,7 @@
       </c>
       <c r="D348" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E348" t="inlineStr">
@@ -47062,7 +47062,7 @@
       </c>
       <c r="D369" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E369" t="inlineStr">
@@ -47158,7 +47158,7 @@
       </c>
       <c r="D370" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E370" t="inlineStr">
@@ -49574,7 +49574,7 @@
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>BasicAverageShares</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
@@ -51004,7 +51004,7 @@
       </c>
       <c r="D408" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E408" t="inlineStr">
@@ -52238,7 +52238,7 @@
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
@@ -53566,7 +53566,7 @@
       </c>
       <c r="D433" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E433" t="inlineStr">
@@ -55614,7 +55614,7 @@
       </c>
       <c r="D453" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E453" t="inlineStr">
@@ -56964,7 +56964,7 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
@@ -59700,7 +59700,7 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">

--- a/output/pdf_financials_xlsx/ERD.xlsx
+++ b/output/pdf_financials_xlsx/ERD.xlsx
@@ -28180,7 +28180,11 @@
           <t>Issue of common shares, net of issue costs 10</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -29114,7 +29118,11 @@
           <t>Issue of common shares, net of issue costs 11</t>
         </is>
       </c>
-      <c r="D197" t="inlineStr"/>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E197" t="inlineStr">
         <is>
           <t>-</t>
@@ -30142,7 +30150,11 @@
           <t>Issue of common shares, net of issue costs 12</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr"/>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E207" t="inlineStr">
         <is>
           <t>-</t>
@@ -31532,7 +31544,11 @@
           <t>Issue of common shares, net of issue costs 10</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>IssuanceOfCapitalStock</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
